--- a/astro-site/public/dl/kit-gestion-personal/05-planificacion-vacaciones.xlsx
+++ b/astro-site/public/dl/kit-gestion-personal/05-planificacion-vacaciones.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Calendario Anual" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Solicitudes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cobertura" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario Anual" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Solicitudes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Calendario Anual'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Solicitudes'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Cobertura'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt formatCode="DD/MM/YYYY" numFmtId="164"/>
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -160,38 +164,38 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="7" fontId="8" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -551,15 +555,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -567,6 +572,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -602,9 +608,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -640,9 +644,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" t="inlineStr"/>
-    </row>
+    <row r="15"/>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
         <is>
@@ -657,8 +659,25 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-gestion-personal · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -667,25 +686,25 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="20"/>
-    <col customWidth="1" max="2" min="2" width="8"/>
-    <col customWidth="1" max="3" min="3" width="8"/>
-    <col customWidth="1" max="4" min="4" width="8"/>
-    <col customWidth="1" max="5" min="5" width="8"/>
-    <col customWidth="1" max="6" min="6" width="8"/>
-    <col customWidth="1" max="7" min="7" width="8"/>
-    <col customWidth="1" max="8" min="8" width="8"/>
-    <col customWidth="1" max="9" min="9" width="8"/>
-    <col customWidth="1" max="10" min="10" width="8"/>
-    <col customWidth="1" max="11" min="11" width="8"/>
-    <col customWidth="1" max="12" min="12" width="8"/>
-    <col customWidth="1" max="13" min="13" width="8"/>
-    <col customWidth="1" max="14" min="14" width="14"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -724,6 +743,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -812,7 +832,7 @@
       <c r="M6" s="12" t="n"/>
       <c r="N6" s="13">
         <f>IF(B6="V",1,0)+IF(C6="V",1,0)+IF(D6="V",1,0)+IF(E6="V",1,0)+IF(F6="V",1,0)+IF(G6="V",1,0)+IF(H6="V",1,0)+IF(I6="V",1,0)+IF(J6="V",1,0)+IF(K6="V",1,0)+IF(L6="V",1,0)+IF(M6="V",1,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -831,7 +851,7 @@
       <c r="M7" s="12" t="n"/>
       <c r="N7" s="13">
         <f>IF(B7="V",1,0)+IF(C7="V",1,0)+IF(D7="V",1,0)+IF(E7="V",1,0)+IF(F7="V",1,0)+IF(G7="V",1,0)+IF(H7="V",1,0)+IF(I7="V",1,0)+IF(J7="V",1,0)+IF(K7="V",1,0)+IF(L7="V",1,0)+IF(M7="V",1,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8">
@@ -850,7 +870,7 @@
       <c r="M8" s="12" t="n"/>
       <c r="N8" s="13">
         <f>IF(B8="V",1,0)+IF(C8="V",1,0)+IF(D8="V",1,0)+IF(E8="V",1,0)+IF(F8="V",1,0)+IF(G8="V",1,0)+IF(H8="V",1,0)+IF(I8="V",1,0)+IF(J8="V",1,0)+IF(K8="V",1,0)+IF(L8="V",1,0)+IF(M8="V",1,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9">
@@ -869,7 +889,7 @@
       <c r="M9" s="12" t="n"/>
       <c r="N9" s="13">
         <f>IF(B9="V",1,0)+IF(C9="V",1,0)+IF(D9="V",1,0)+IF(E9="V",1,0)+IF(F9="V",1,0)+IF(G9="V",1,0)+IF(H9="V",1,0)+IF(I9="V",1,0)+IF(J9="V",1,0)+IF(K9="V",1,0)+IF(L9="V",1,0)+IF(M9="V",1,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -888,7 +908,7 @@
       <c r="M10" s="12" t="n"/>
       <c r="N10" s="13">
         <f>IF(B10="V",1,0)+IF(C10="V",1,0)+IF(D10="V",1,0)+IF(E10="V",1,0)+IF(F10="V",1,0)+IF(G10="V",1,0)+IF(H10="V",1,0)+IF(I10="V",1,0)+IF(J10="V",1,0)+IF(K10="V",1,0)+IF(L10="V",1,0)+IF(M10="V",1,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="11">
@@ -907,7 +927,7 @@
       <c r="M11" s="12" t="n"/>
       <c r="N11" s="13">
         <f>IF(B11="V",1,0)+IF(C11="V",1,0)+IF(D11="V",1,0)+IF(E11="V",1,0)+IF(F11="V",1,0)+IF(G11="V",1,0)+IF(H11="V",1,0)+IF(I11="V",1,0)+IF(J11="V",1,0)+IF(K11="V",1,0)+IF(L11="V",1,0)+IF(M11="V",1,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +946,7 @@
       <c r="M12" s="12" t="n"/>
       <c r="N12" s="13">
         <f>IF(B12="V",1,0)+IF(C12="V",1,0)+IF(D12="V",1,0)+IF(E12="V",1,0)+IF(F12="V",1,0)+IF(G12="V",1,0)+IF(H12="V",1,0)+IF(I12="V",1,0)+IF(J12="V",1,0)+IF(K12="V",1,0)+IF(L12="V",1,0)+IF(M12="V",1,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
@@ -945,7 +965,7 @@
       <c r="M13" s="12" t="n"/>
       <c r="N13" s="13">
         <f>IF(B13="V",1,0)+IF(C13="V",1,0)+IF(D13="V",1,0)+IF(E13="V",1,0)+IF(F13="V",1,0)+IF(G13="V",1,0)+IF(H13="V",1,0)+IF(I13="V",1,0)+IF(J13="V",1,0)+IF(K13="V",1,0)+IF(L13="V",1,0)+IF(M13="V",1,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
@@ -964,7 +984,7 @@
       <c r="M14" s="12" t="n"/>
       <c r="N14" s="13">
         <f>IF(B14="V",1,0)+IF(C14="V",1,0)+IF(D14="V",1,0)+IF(E14="V",1,0)+IF(F14="V",1,0)+IF(G14="V",1,0)+IF(H14="V",1,0)+IF(I14="V",1,0)+IF(J14="V",1,0)+IF(K14="V",1,0)+IF(L14="V",1,0)+IF(M14="V",1,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -983,7 +1003,7 @@
       <c r="M15" s="12" t="n"/>
       <c r="N15" s="13">
         <f>IF(B15="V",1,0)+IF(C15="V",1,0)+IF(D15="V",1,0)+IF(E15="V",1,0)+IF(F15="V",1,0)+IF(G15="V",1,0)+IF(H15="V",1,0)+IF(I15="V",1,0)+IF(J15="V",1,0)+IF(K15="V",1,0)+IF(L15="V",1,0)+IF(M15="V",1,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16">
@@ -1002,7 +1022,7 @@
       <c r="M16" s="12" t="n"/>
       <c r="N16" s="13">
         <f>IF(B16="V",1,0)+IF(C16="V",1,0)+IF(D16="V",1,0)+IF(E16="V",1,0)+IF(F16="V",1,0)+IF(G16="V",1,0)+IF(H16="V",1,0)+IF(I16="V",1,0)+IF(J16="V",1,0)+IF(K16="V",1,0)+IF(L16="V",1,0)+IF(M16="V",1,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
@@ -1021,7 +1041,7 @@
       <c r="M17" s="12" t="n"/>
       <c r="N17" s="13">
         <f>IF(B17="V",1,0)+IF(C17="V",1,0)+IF(D17="V",1,0)+IF(E17="V",1,0)+IF(F17="V",1,0)+IF(G17="V",1,0)+IF(H17="V",1,0)+IF(I17="V",1,0)+IF(J17="V",1,0)+IF(K17="V",1,0)+IF(L17="V",1,0)+IF(M17="V",1,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="18">
@@ -1040,7 +1060,7 @@
       <c r="M18" s="12" t="n"/>
       <c r="N18" s="13">
         <f>IF(B18="V",1,0)+IF(C18="V",1,0)+IF(D18="V",1,0)+IF(E18="V",1,0)+IF(F18="V",1,0)+IF(G18="V",1,0)+IF(H18="V",1,0)+IF(I18="V",1,0)+IF(J18="V",1,0)+IF(K18="V",1,0)+IF(L18="V",1,0)+IF(M18="V",1,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="19">
@@ -1059,7 +1079,7 @@
       <c r="M19" s="12" t="n"/>
       <c r="N19" s="13">
         <f>IF(B19="V",1,0)+IF(C19="V",1,0)+IF(D19="V",1,0)+IF(E19="V",1,0)+IF(F19="V",1,0)+IF(G19="V",1,0)+IF(H19="V",1,0)+IF(I19="V",1,0)+IF(J19="V",1,0)+IF(K19="V",1,0)+IF(L19="V",1,0)+IF(M19="V",1,0)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="20">
@@ -1078,9 +1098,11 @@
       <c r="M20" s="12" t="n"/>
       <c r="N20" s="13">
         <f>IF(B20="V",1,0)+IF(C20="V",1,0)+IF(D20="V",1,0)+IF(E20="V",1,0)+IF(F20="V",1,0)+IF(G20="V",1,0)+IF(H20="V",1,0)+IF(I20="V",1,0)+IF(J20="V",1,0)+IF(K20="V",1,0)+IF(L20="V",1,0)+IF(M20="V",1,0)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
@@ -1095,11 +1117,20 @@
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20" type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"V,B,F,P,"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1108,18 +1139,18 @@
   <sheetPr>
     <tabColor rgb="000D47A1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="22"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="16"/>
-    <col customWidth="1" max="7" min="7" width="18"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1136,6 +1167,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1623,6 +1655,7 @@
       </c>
       <c r="G34" s="12" t="n"/>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
@@ -1637,11 +1670,20 @@
     <mergeCell ref="A2:G2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34" type="list">
+    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,Aprobado,Denegado"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1650,16 +1692,16 @@
   <sheetPr>
     <tabColor rgb="004CAF50"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="22"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="22"/>
-    <col customWidth="1" max="4" min="4" width="22"/>
-    <col customWidth="1" max="5" min="5" width="20"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1676,6 +1718,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -1743,6 +1786,7 @@
       <c r="D8" s="12" t="n"/>
       <c r="E8" s="12" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
@@ -1882,6 +1926,8 @@
       <c r="D26" s="11" t="n"/>
       <c r="E26" s="11" t="n"/>
     </row>
+    <row r="27"/>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
@@ -1895,6 +1941,15 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-gestion-personal/05-planificacion-vacaciones.xlsx
+++ b/astro-site/public/dl/kit-gestion-personal/05-planificacion-vacaciones.xlsx
@@ -1,22 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario Anual" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Solicitudes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Calendario Anual" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Solicitudes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Cobertura" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Calendario Anual'!$5:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Solicitudes'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Cobertura'!$5:$5</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -24,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+    <numFmt formatCode="DD/MM/YYYY" numFmtId="164"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -164,38 +160,38 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="5" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="6" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf borderId="1" fillId="7" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="7" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="7" fontId="8" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -555,16 +551,15 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="B2:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col customWidth="1" max="1" min="1" width="3"/>
+    <col customWidth="1" max="2" min="2" width="80"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -572,7 +567,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -608,7 +602,9 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="9">
+      <c r="B9" t="inlineStr"/>
+    </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -644,7 +640,9 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
+    <row r="15">
+      <c r="B15" t="inlineStr"/>
+    </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
         <is>
@@ -659,25 +657,8 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-gestion-personal · info@aichef.pro</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
 
@@ -686,25 +667,25 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col customWidth="1" max="1" min="1" width="20"/>
+    <col customWidth="1" max="2" min="2" width="8"/>
+    <col customWidth="1" max="3" min="3" width="8"/>
+    <col customWidth="1" max="4" min="4" width="8"/>
+    <col customWidth="1" max="5" min="5" width="8"/>
+    <col customWidth="1" max="6" min="6" width="8"/>
+    <col customWidth="1" max="7" min="7" width="8"/>
+    <col customWidth="1" max="8" min="8" width="8"/>
+    <col customWidth="1" max="9" min="9" width="8"/>
+    <col customWidth="1" max="10" min="10" width="8"/>
+    <col customWidth="1" max="11" min="11" width="8"/>
+    <col customWidth="1" max="12" min="12" width="8"/>
+    <col customWidth="1" max="13" min="13" width="8"/>
+    <col customWidth="1" max="14" min="14" width="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -743,7 +724,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -832,7 +812,7 @@
       <c r="M6" s="12" t="n"/>
       <c r="N6" s="13">
         <f>IF(B6="V",1,0)+IF(C6="V",1,0)+IF(D6="V",1,0)+IF(E6="V",1,0)+IF(F6="V",1,0)+IF(G6="V",1,0)+IF(H6="V",1,0)+IF(I6="V",1,0)+IF(J6="V",1,0)+IF(K6="V",1,0)+IF(L6="V",1,0)+IF(M6="V",1,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -851,7 +831,7 @@
       <c r="M7" s="12" t="n"/>
       <c r="N7" s="13">
         <f>IF(B7="V",1,0)+IF(C7="V",1,0)+IF(D7="V",1,0)+IF(E7="V",1,0)+IF(F7="V",1,0)+IF(G7="V",1,0)+IF(H7="V",1,0)+IF(I7="V",1,0)+IF(J7="V",1,0)+IF(K7="V",1,0)+IF(L7="V",1,0)+IF(M7="V",1,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -870,7 +850,7 @@
       <c r="M8" s="12" t="n"/>
       <c r="N8" s="13">
         <f>IF(B8="V",1,0)+IF(C8="V",1,0)+IF(D8="V",1,0)+IF(E8="V",1,0)+IF(F8="V",1,0)+IF(G8="V",1,0)+IF(H8="V",1,0)+IF(I8="V",1,0)+IF(J8="V",1,0)+IF(K8="V",1,0)+IF(L8="V",1,0)+IF(M8="V",1,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -889,7 +869,7 @@
       <c r="M9" s="12" t="n"/>
       <c r="N9" s="13">
         <f>IF(B9="V",1,0)+IF(C9="V",1,0)+IF(D9="V",1,0)+IF(E9="V",1,0)+IF(F9="V",1,0)+IF(G9="V",1,0)+IF(H9="V",1,0)+IF(I9="V",1,0)+IF(J9="V",1,0)+IF(K9="V",1,0)+IF(L9="V",1,0)+IF(M9="V",1,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -908,7 +888,7 @@
       <c r="M10" s="12" t="n"/>
       <c r="N10" s="13">
         <f>IF(B10="V",1,0)+IF(C10="V",1,0)+IF(D10="V",1,0)+IF(E10="V",1,0)+IF(F10="V",1,0)+IF(G10="V",1,0)+IF(H10="V",1,0)+IF(I10="V",1,0)+IF(J10="V",1,0)+IF(K10="V",1,0)+IF(L10="V",1,0)+IF(M10="V",1,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -927,7 +907,7 @@
       <c r="M11" s="12" t="n"/>
       <c r="N11" s="13">
         <f>IF(B11="V",1,0)+IF(C11="V",1,0)+IF(D11="V",1,0)+IF(E11="V",1,0)+IF(F11="V",1,0)+IF(G11="V",1,0)+IF(H11="V",1,0)+IF(I11="V",1,0)+IF(J11="V",1,0)+IF(K11="V",1,0)+IF(L11="V",1,0)+IF(M11="V",1,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -946,7 +926,7 @@
       <c r="M12" s="12" t="n"/>
       <c r="N12" s="13">
         <f>IF(B12="V",1,0)+IF(C12="V",1,0)+IF(D12="V",1,0)+IF(E12="V",1,0)+IF(F12="V",1,0)+IF(G12="V",1,0)+IF(H12="V",1,0)+IF(I12="V",1,0)+IF(J12="V",1,0)+IF(K12="V",1,0)+IF(L12="V",1,0)+IF(M12="V",1,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -965,7 +945,7 @@
       <c r="M13" s="12" t="n"/>
       <c r="N13" s="13">
         <f>IF(B13="V",1,0)+IF(C13="V",1,0)+IF(D13="V",1,0)+IF(E13="V",1,0)+IF(F13="V",1,0)+IF(G13="V",1,0)+IF(H13="V",1,0)+IF(I13="V",1,0)+IF(J13="V",1,0)+IF(K13="V",1,0)+IF(L13="V",1,0)+IF(M13="V",1,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -984,7 +964,7 @@
       <c r="M14" s="12" t="n"/>
       <c r="N14" s="13">
         <f>IF(B14="V",1,0)+IF(C14="V",1,0)+IF(D14="V",1,0)+IF(E14="V",1,0)+IF(F14="V",1,0)+IF(G14="V",1,0)+IF(H14="V",1,0)+IF(I14="V",1,0)+IF(J14="V",1,0)+IF(K14="V",1,0)+IF(L14="V",1,0)+IF(M14="V",1,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1003,7 +983,7 @@
       <c r="M15" s="12" t="n"/>
       <c r="N15" s="13">
         <f>IF(B15="V",1,0)+IF(C15="V",1,0)+IF(D15="V",1,0)+IF(E15="V",1,0)+IF(F15="V",1,0)+IF(G15="V",1,0)+IF(H15="V",1,0)+IF(I15="V",1,0)+IF(J15="V",1,0)+IF(K15="V",1,0)+IF(L15="V",1,0)+IF(M15="V",1,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1022,7 +1002,7 @@
       <c r="M16" s="12" t="n"/>
       <c r="N16" s="13">
         <f>IF(B16="V",1,0)+IF(C16="V",1,0)+IF(D16="V",1,0)+IF(E16="V",1,0)+IF(F16="V",1,0)+IF(G16="V",1,0)+IF(H16="V",1,0)+IF(I16="V",1,0)+IF(J16="V",1,0)+IF(K16="V",1,0)+IF(L16="V",1,0)+IF(M16="V",1,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -1041,7 +1021,7 @@
       <c r="M17" s="12" t="n"/>
       <c r="N17" s="13">
         <f>IF(B17="V",1,0)+IF(C17="V",1,0)+IF(D17="V",1,0)+IF(E17="V",1,0)+IF(F17="V",1,0)+IF(G17="V",1,0)+IF(H17="V",1,0)+IF(I17="V",1,0)+IF(J17="V",1,0)+IF(K17="V",1,0)+IF(L17="V",1,0)+IF(M17="V",1,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1060,7 +1040,7 @@
       <c r="M18" s="12" t="n"/>
       <c r="N18" s="13">
         <f>IF(B18="V",1,0)+IF(C18="V",1,0)+IF(D18="V",1,0)+IF(E18="V",1,0)+IF(F18="V",1,0)+IF(G18="V",1,0)+IF(H18="V",1,0)+IF(I18="V",1,0)+IF(J18="V",1,0)+IF(K18="V",1,0)+IF(L18="V",1,0)+IF(M18="V",1,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1079,7 +1059,7 @@
       <c r="M19" s="12" t="n"/>
       <c r="N19" s="13">
         <f>IF(B19="V",1,0)+IF(C19="V",1,0)+IF(D19="V",1,0)+IF(E19="V",1,0)+IF(F19="V",1,0)+IF(G19="V",1,0)+IF(H19="V",1,0)+IF(I19="V",1,0)+IF(J19="V",1,0)+IF(K19="V",1,0)+IF(L19="V",1,0)+IF(M19="V",1,0)</f>
-        <v>0.0</v>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -1098,11 +1078,9 @@
       <c r="M20" s="12" t="n"/>
       <c r="N20" s="13">
         <f>IF(B20="V",1,0)+IF(C20="V",1,0)+IF(D20="V",1,0)+IF(E20="V",1,0)+IF(F20="V",1,0)+IF(G20="V",1,0)+IF(H20="V",1,0)+IF(I20="V",1,0)+IF(J20="V",1,0)+IF(K20="V",1,0)+IF(L20="V",1,0)+IF(M20="V",1,0)</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22"/>
+        <v/>
+      </c>
+    </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
@@ -1117,20 +1095,11 @@
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20" type="list">
       <formula1>"V,B,F,P,"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
 
@@ -1139,18 +1108,18 @@
   <sheetPr>
     <tabColor rgb="000D47A1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col customWidth="1" max="1" min="1" width="22"/>
+    <col customWidth="1" max="2" min="2" width="16"/>
+    <col customWidth="1" max="3" min="3" width="16"/>
+    <col customWidth="1" max="4" min="4" width="14"/>
+    <col customWidth="1" max="5" min="5" width="14"/>
+    <col customWidth="1" max="6" min="6" width="16"/>
+    <col customWidth="1" max="7" min="7" width="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1167,7 +1136,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1655,7 +1623,6 @@
       </c>
       <c r="G34" s="12" t="n"/>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
@@ -1670,20 +1637,11 @@
     <mergeCell ref="A2:G2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34" type="list">
       <formula1>"Pendiente,Aprobado,Denegado"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
 
@@ -1692,16 +1650,16 @@
   <sheetPr>
     <tabColor rgb="004CAF50"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col customWidth="1" max="1" min="1" width="22"/>
+    <col customWidth="1" max="2" min="2" width="16"/>
+    <col customWidth="1" max="3" min="3" width="22"/>
+    <col customWidth="1" max="4" min="4" width="22"/>
+    <col customWidth="1" max="5" min="5" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1718,7 +1676,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -1786,7 +1743,6 @@
       <c r="D8" s="12" t="n"/>
       <c r="E8" s="12" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
@@ -1926,8 +1882,6 @@
       <c r="D26" s="11" t="n"/>
       <c r="E26" s="11" t="n"/>
     </row>
-    <row r="27"/>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
@@ -1941,15 +1895,6 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>